--- a/data/trans_bre/IP07_R2-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP07_R2-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7,83</t>
+          <t>2,22</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>136,65%</t>
+          <t>36,66%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 9,35</t>
+          <t>-2,28; 9,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 7,07</t>
+          <t>-6,55; 6,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 10,54</t>
+          <t>-6,26; 9,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 29,57</t>
+          <t>-5,03; 10,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,17 +685,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-85,65; 422,75</t>
+          <t>-85,87; 428,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-63,7; 421,54</t>
+          <t>-67,58; 318,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-44,87; 1043,38</t>
+          <t>-60,19; 395,6</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,08</t>
+          <t>1,91</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>62,37%</t>
+          <t>113,28%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 1,23</t>
+          <t>-6,02; 1,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 2,56</t>
+          <t>-5,13; 3,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 2,85</t>
+          <t>-5,37; 2,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 4,99</t>
+          <t>-1,18; 6,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 104,1</t>
+          <t>-100,0; 103,96</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-84,91; 121,82</t>
+          <t>-85,16; 146,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 282,61</t>
+          <t>-100,0; 297,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-91,32; 1197,05</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-2,27</t>
+          <t>-2,32</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 2,24</t>
+          <t>-5,26; 2,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 3,3</t>
+          <t>-1,84; 4,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 0,0</t>
+          <t>-8,23; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,2</t>
+          <t>2,08</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>117,71%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,77; -0,85</t>
+          <t>-8,39; -0,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 7,41</t>
+          <t>-1,0; 6,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 5,51</t>
+          <t>-3,55; 6,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 7,42</t>
+          <t>-4,43; 8,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-77,72; 517,48</t>
+          <t>-72,65; 534,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,11</t>
+          <t>0,02</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,97; 5,69</t>
+          <t>-11,72; 4,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-14,55; -1,51</t>
+          <t>-14,71; -2,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 4,95</t>
+          <t>-2,95; 5,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 294,45</t>
+          <t>-100,0; 201,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-1,52</t>
+          <t>-1,63</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-51,28%</t>
+          <t>-53,95%</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 2,39</t>
+          <t>-4,33; 2,45</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 3,99</t>
+          <t>-2,36; 4,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 2,37</t>
+          <t>-4,57; 2,32</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 2,56</t>
+          <t>-7,38; 2,31</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-1,52</t>
+          <t>-1,57</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-41,27%</t>
+          <t>-41,09%</t>
         </is>
       </c>
     </row>
@@ -1260,32 +1260,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 0,61</t>
+          <t>-4,6; 0,65</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 1,95</t>
+          <t>-2,6; 2,07</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 0,98</t>
+          <t>-3,3; 1,06</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 2,07</t>
+          <t>-5,57; 2,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 221,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 351,8</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-90,52; 175,04</t>
+          <t>-93,16; 170,9</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,08</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>13,25%</t>
         </is>
       </c>
     </row>
@@ -1360,32 +1360,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 0,01</t>
+          <t>-5,88; -0,23</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 4,04</t>
+          <t>-1,49; 3,99</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 1,25</t>
+          <t>-1,77; 0,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 2,17</t>
+          <t>-1,2; 2,11</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-92,32; 24,64</t>
+          <t>-92,41; 13,41</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-66,27; 667,52</t>
+          <t>-62,52; 946,39</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>0,72</t>
+          <t>0,12</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,14; -0,52</t>
+          <t>-3,3; -0,54</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 1,2</t>
+          <t>-1,45; 1,22</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 1,07</t>
+          <t>-1,38; 1,02</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 3,91</t>
+          <t>-1,53; 1,54</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-72,74; -13,8</t>
+          <t>-74,28; -14,75</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-46,71; 64,05</t>
+          <t>-47,45; 72,13</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-50,0; 74,47</t>
+          <t>-51,57; 70,58</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-32,22; 182,94</t>
+          <t>-46,82; 92,64</t>
         </is>
       </c>
     </row>
